--- a/todos.xlsx
+++ b/todos.xlsx
@@ -418,36 +418,36 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7c629a3f-b55a-414a-b8db-6856bac3a549</v>
+        <v>35bb0708-d049-4111-b21d-844216fbdc33</v>
       </c>
       <c r="B2" t="str">
-        <v>new to do</v>
+        <v>new to</v>
       </c>
       <c r="C2" t="str">
         <v>doing</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-11T13:58:06.228Z</v>
+        <v>2026-06-14T20:43:48.762Z</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-06-11T13:58:06.228Z</v>
+        <v>2026-06-14T20:55:31.195Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>4dd93d1f-4844-4052-aa6d-0da935024944</v>
+        <v>61642022-4fcc-4c0a-9cb2-f0b05f13f9ab</v>
       </c>
       <c r="B3" t="str">
-        <v>new to do</v>
+        <v>new to added</v>
       </c>
       <c r="C3" t="str">
         <v>doing</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-11T13:58:46.308Z</v>
+        <v>2026-06-14T20:59:51.224Z</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-06-11T13:58:46.308Z</v>
+        <v>2026-06-14T20:59:51.224Z</v>
       </c>
     </row>
   </sheetData>
